--- a/Results/Results.out/Goats/reg_out_goat_hin.all.xlsx
+++ b/Results/Results.out/Goats/reg_out_goat_hin.all.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="469">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -113,6 +113,12 @@
     <t xml:space="preserve">coef.BW</t>
   </si>
   <si>
+    <t xml:space="preserve">coef.MBW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coef.BW.fM</t>
+  </si>
+  <si>
     <t xml:space="preserve">coef.ADG</t>
   </si>
   <si>
@@ -344,6 +350,42 @@
     <t xml:space="preserve">ws.coef.bw_kg.cbd</t>
   </si>
   <si>
+    <t xml:space="preserve">ws.coef.Met_bw_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.Met_bw_kg.e25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.Met_bw_kg.sqt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.Met_bw_kg.e75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.Met_bw_kg.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.Met_bw_kg.cbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.bw_frac_Mat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.bw_frac_Mat.e25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.bw_frac_Mat.sqt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.bw_frac_Mat.e75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.bw_frac_Mat.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.bw_frac_Mat.cbd</t>
+  </si>
+  <si>
     <t xml:space="preserve">ws.coef.adg_kg_day</t>
   </si>
   <si>
@@ -584,6 +626,42 @@
     <t xml:space="preserve">ws.coef.se.bw_kg.cbd</t>
   </si>
   <si>
+    <t xml:space="preserve">ws.coef.se.Met_bw_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.Met_bw_kg.e25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.Met_bw_kg.sqt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.Met_bw_kg.e75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.Met_bw_kg.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.Met_bw_kg.cbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.bw_frac_Mat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.bw_frac_Mat.e25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.bw_frac_Mat.sqt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.bw_frac_Mat.e75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.bw_frac_Mat.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.bw_frac_Mat.cbd</t>
+  </si>
+  <si>
     <t xml:space="preserve">ws.coef.se.adg_kg_day</t>
   </si>
   <si>
@@ -836,6 +914,42 @@
     <t xml:space="preserve">ws.coef.sign.bw_kg.cbd</t>
   </si>
   <si>
+    <t xml:space="preserve">ws.coef.sign.Met_bw_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.sign.Met_bw_kg.e25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.sign.Met_bw_kg.sqt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.sign.Met_bw_kg.e75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.sign.Met_bw_kg.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.sign.Met_bw_kg.cbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.sign.BW_frac_Mat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.sign.BW_frac_Mat.e25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.sign.BW_frac_Mat.sqt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.sign.BW_frac_Mat.e75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.sign.BW_frac_Mat.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.sign.BW_frac_Mat.cbd</t>
+  </si>
+  <si>
     <t xml:space="preserve">ws.coef.sign.adg_kg_day</t>
   </si>
   <si>
@@ -1073,6 +1187,12 @@
     <t xml:space="preserve">vif.bw_kg</t>
   </si>
   <si>
+    <t xml:space="preserve">vif.Met_bw_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vif.BW_frac_Mat</t>
+  </si>
+  <si>
     <t xml:space="preserve">vif.ADG</t>
   </si>
   <si>
@@ -1115,6 +1235,12 @@
     <t xml:space="preserve">mean.var.imp.BW</t>
   </si>
   <si>
+    <t xml:space="preserve">mean.var.imp.MBW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.BW.fM</t>
+  </si>
+  <si>
     <t xml:space="preserve">mean.var.imp.ADG</t>
   </si>
   <si>
@@ -1145,6 +1271,12 @@
     <t xml:space="preserve">mean.var.rel.imp.BW</t>
   </si>
   <si>
+    <t xml:space="preserve">mean.var.rel.imp.MBW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.rel.imp.BW.fM</t>
+  </si>
+  <si>
     <t xml:space="preserve">mean.var.rel.imp.ADG</t>
   </si>
   <si>
@@ -1175,6 +1307,12 @@
     <t xml:space="preserve">sd.rel.var.imp.BW</t>
   </si>
   <si>
+    <t xml:space="preserve">sd.rel.var.imp.MBW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.rel.var.imp.BW.fM</t>
+  </si>
+  <si>
     <t xml:space="preserve">sd.rel.var.imp.ADG</t>
   </si>
   <si>
@@ -1203,6 +1341,12 @@
   </si>
   <si>
     <t xml:space="preserve">sd.var.imp.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.var.imp.MBW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.var.imp.BW.fM</t>
   </si>
   <si>
     <t xml:space="preserve">sd.var.imp.ADG</t>
@@ -2867,6 +3011,150 @@
       <c r="PE1" t="s">
         <v>420</v>
       </c>
+      <c r="PF1" t="s">
+        <v>421</v>
+      </c>
+      <c r="PG1" t="s">
+        <v>422</v>
+      </c>
+      <c r="PH1" t="s">
+        <v>423</v>
+      </c>
+      <c r="PI1" t="s">
+        <v>424</v>
+      </c>
+      <c r="PJ1" t="s">
+        <v>425</v>
+      </c>
+      <c r="PK1" t="s">
+        <v>426</v>
+      </c>
+      <c r="PL1" t="s">
+        <v>427</v>
+      </c>
+      <c r="PM1" t="s">
+        <v>428</v>
+      </c>
+      <c r="PN1" t="s">
+        <v>429</v>
+      </c>
+      <c r="PO1" t="s">
+        <v>430</v>
+      </c>
+      <c r="PP1" t="s">
+        <v>431</v>
+      </c>
+      <c r="PQ1" t="s">
+        <v>432</v>
+      </c>
+      <c r="PR1" t="s">
+        <v>433</v>
+      </c>
+      <c r="PS1" t="s">
+        <v>434</v>
+      </c>
+      <c r="PT1" t="s">
+        <v>435</v>
+      </c>
+      <c r="PU1" t="s">
+        <v>436</v>
+      </c>
+      <c r="PV1" t="s">
+        <v>437</v>
+      </c>
+      <c r="PW1" t="s">
+        <v>438</v>
+      </c>
+      <c r="PX1" t="s">
+        <v>439</v>
+      </c>
+      <c r="PY1" t="s">
+        <v>440</v>
+      </c>
+      <c r="PZ1" t="s">
+        <v>441</v>
+      </c>
+      <c r="QA1" t="s">
+        <v>442</v>
+      </c>
+      <c r="QB1" t="s">
+        <v>443</v>
+      </c>
+      <c r="QC1" t="s">
+        <v>444</v>
+      </c>
+      <c r="QD1" t="s">
+        <v>445</v>
+      </c>
+      <c r="QE1" t="s">
+        <v>446</v>
+      </c>
+      <c r="QF1" t="s">
+        <v>447</v>
+      </c>
+      <c r="QG1" t="s">
+        <v>448</v>
+      </c>
+      <c r="QH1" t="s">
+        <v>449</v>
+      </c>
+      <c r="QI1" t="s">
+        <v>450</v>
+      </c>
+      <c r="QJ1" t="s">
+        <v>451</v>
+      </c>
+      <c r="QK1" t="s">
+        <v>452</v>
+      </c>
+      <c r="QL1" t="s">
+        <v>453</v>
+      </c>
+      <c r="QM1" t="s">
+        <v>454</v>
+      </c>
+      <c r="QN1" t="s">
+        <v>455</v>
+      </c>
+      <c r="QO1" t="s">
+        <v>456</v>
+      </c>
+      <c r="QP1" t="s">
+        <v>457</v>
+      </c>
+      <c r="QQ1" t="s">
+        <v>458</v>
+      </c>
+      <c r="QR1" t="s">
+        <v>459</v>
+      </c>
+      <c r="QS1" t="s">
+        <v>460</v>
+      </c>
+      <c r="QT1" t="s">
+        <v>461</v>
+      </c>
+      <c r="QU1" t="s">
+        <v>462</v>
+      </c>
+      <c r="QV1" t="s">
+        <v>463</v>
+      </c>
+      <c r="QW1" t="s">
+        <v>464</v>
+      </c>
+      <c r="QX1" t="s">
+        <v>465</v>
+      </c>
+      <c r="QY1" t="s">
+        <v>466</v>
+      </c>
+      <c r="QZ1" t="s">
+        <v>467</v>
+      </c>
+      <c r="RA1" t="s">
+        <v>468</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
